--- a/site/ValueSet-vs-localidades-uy.xlsx
+++ b/site/ValueSet-vs-localidades-uy.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="486">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T15:20:04-03:00</t>
+    <t>2026-10-06T01:23:13-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -66,6 +66,12 @@
     <t>AGESIC</t>
   </si>
   <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>AGESIC (https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/salud-digital)</t>
+  </si>
+  <si>
     <t>Jurisdiction</t>
   </si>
   <si>
@@ -90,10 +96,1375 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>18 DE JULIO</t>
+  </si>
+  <si>
+    <t>19 DE ABRIL</t>
+  </si>
+  <si>
+    <t>25 DE AGOSTO</t>
+  </si>
+  <si>
+    <t>25 DE MAYO</t>
+  </si>
+  <si>
+    <t>ABROJAL</t>
+  </si>
+  <si>
+    <t>ACEGUA</t>
+  </si>
+  <si>
+    <t>ACHAR</t>
+  </si>
+  <si>
+    <t>AEROPARQUE</t>
+  </si>
+  <si>
+    <t>AGRACIADA</t>
+  </si>
+  <si>
+    <t>AGUAS BLANCAS</t>
+  </si>
+  <si>
+    <t>AGUAS BUENAS</t>
+  </si>
+  <si>
+    <t>AGUAS CTES.</t>
+  </si>
+  <si>
+    <t>AGUAS DULCES</t>
+  </si>
+  <si>
+    <t>AIGUA</t>
+  </si>
+  <si>
+    <t>ALGORTA</t>
+  </si>
+  <si>
+    <t>AMARILLO</t>
+  </si>
+  <si>
+    <t>ANDRESITO</t>
+  </si>
+  <si>
+    <t>ANTONIOPOLIS</t>
+  </si>
+  <si>
+    <t>ARAMENDIA</t>
+  </si>
+  <si>
+    <t>ARAMINDA</t>
+  </si>
+  <si>
+    <t>ARBOLITO1</t>
+  </si>
+  <si>
+    <t>ARBOLITO2</t>
+  </si>
+  <si>
+    <t>ARENITAS BLANCA</t>
+  </si>
+  <si>
+    <t>ARROYO BLANCO</t>
+  </si>
+  <si>
+    <t>ARTIGAS</t>
+  </si>
+  <si>
+    <t>ARTILLEROS</t>
+  </si>
+  <si>
+    <t>ATLANTIDA</t>
+  </si>
+  <si>
+    <t>AUTODROMO</t>
+  </si>
+  <si>
+    <t>AYUI</t>
+  </si>
+  <si>
+    <t>B. BRUM</t>
+  </si>
+  <si>
+    <t>B. RIVERA</t>
+  </si>
+  <si>
+    <t>B.BLANCOS</t>
+  </si>
+  <si>
+    <t>BALNEARIO BUENOS AIRES (ADCL)</t>
+  </si>
+  <si>
+    <t>BAÑADO DE MEDIN</t>
+  </si>
+  <si>
+    <t>BARRA CARRASCO</t>
+  </si>
+  <si>
+    <t>BARRA CHUY</t>
+  </si>
+  <si>
+    <t>BARRA D VALIZAS</t>
+  </si>
+  <si>
+    <t>BARRA URUGUAYA</t>
+  </si>
+  <si>
+    <t>BARRIO ARTIGAS</t>
+  </si>
+  <si>
+    <t>BATLLE Y ORDOÑEZ</t>
+  </si>
+  <si>
+    <t>BELEN</t>
+  </si>
+  <si>
+    <t>BELLA UNION</t>
+  </si>
+  <si>
+    <t>BELLO HORIZONTE</t>
+  </si>
+  <si>
+    <t>BERRONDO</t>
+  </si>
+  <si>
+    <t>BIARRITZ</t>
+  </si>
+  <si>
+    <t>BIASSINI</t>
+  </si>
+  <si>
+    <t>BLANCA ARENA</t>
+  </si>
+  <si>
+    <t>BLANQUILLO</t>
+  </si>
+  <si>
+    <t>BOCA DEL CUFRE</t>
+  </si>
+  <si>
+    <t>BOLIVAR</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>BRIO. ARGENTINO</t>
+  </si>
+  <si>
+    <t>BRIO. BUENOS AIRES</t>
+  </si>
+  <si>
+    <t>BRIO.ESPAÑOL</t>
+  </si>
+  <si>
+    <t>BRISAS DE PLATA</t>
+  </si>
+  <si>
+    <t>BRITOPOLIS</t>
+  </si>
+  <si>
+    <t>BRRA DE LOS CHANCHOS</t>
+  </si>
+  <si>
+    <t>BRRIO PINTADITO</t>
+  </si>
+  <si>
+    <t>BRRIO.ALBISU</t>
+  </si>
+  <si>
+    <t>BURICAYUPI</t>
+  </si>
+  <si>
+    <t>C. DEL PERDIDO</t>
+  </si>
+  <si>
+    <t>C.COLORADO</t>
+  </si>
+  <si>
+    <t>C.MIGUELETE</t>
+  </si>
+  <si>
+    <t>C.REYLES</t>
+  </si>
+  <si>
+    <t>C.ROSSEL</t>
+  </si>
+  <si>
+    <t>C.VALDENSE</t>
+  </si>
+  <si>
+    <t>CAMPAMENTO</t>
+  </si>
+  <si>
+    <t>CANELONES</t>
+  </si>
+  <si>
+    <t>CAÑADA DEL ESTADO</t>
+  </si>
+  <si>
+    <t>CAÑADA MILAN</t>
+  </si>
+  <si>
+    <t>CAÑADA NIETO</t>
+  </si>
+  <si>
+    <t>CAP. FARRUCO</t>
+  </si>
+  <si>
+    <t>CAPILLA D CELLA</t>
+  </si>
+  <si>
+    <t>CAPURRO</t>
+  </si>
+  <si>
+    <t>CARAGUATA NORTE</t>
+  </si>
+  <si>
+    <t>CARDAL</t>
+  </si>
+  <si>
+    <t>CARDONA</t>
+  </si>
+  <si>
+    <t>CARDOZO CHICO</t>
+  </si>
+  <si>
+    <t>CARDOZO GRANDE</t>
+  </si>
+  <si>
+    <t>CARMELO</t>
+  </si>
+  <si>
+    <t>CARRETA QUEMADA</t>
+  </si>
+  <si>
+    <t>CASTILLOS</t>
+  </si>
+  <si>
+    <t>CASUPA</t>
+  </si>
+  <si>
+    <t>CDAD.DEL PLATA</t>
+  </si>
+  <si>
+    <t>CEBOLLATI</t>
+  </si>
+  <si>
+    <t>CERRILLADA</t>
+  </si>
+  <si>
+    <t>CERRILLOS</t>
+  </si>
+  <si>
+    <t>CERRO CHATO1</t>
+  </si>
+  <si>
+    <t>CERRO CHATO2</t>
+  </si>
+  <si>
+    <t>CERRO COLORADO</t>
+  </si>
+  <si>
+    <t>CERRO CUENTAS</t>
+  </si>
+  <si>
+    <t>CERRO DEL ARBOLITO</t>
+  </si>
+  <si>
+    <t>CERRO EJIDO</t>
+  </si>
+  <si>
+    <t>CERRO PELADO</t>
+  </si>
+  <si>
+    <t>CERRO PEREYRA</t>
+  </si>
+  <si>
+    <t>CERROS AZULES</t>
+  </si>
+  <si>
+    <t>CERROS BLANCOS</t>
+  </si>
+  <si>
+    <t>CHAMBERLAIN</t>
+  </si>
+  <si>
+    <t>CHAMIZO</t>
+  </si>
+  <si>
+    <t>CHAPICUY</t>
+  </si>
+  <si>
+    <t>CHINGOLAS</t>
+  </si>
+  <si>
+    <t>CHUY</t>
+  </si>
+  <si>
+    <t>CLARA</t>
+  </si>
+  <si>
+    <t>COLINAS</t>
+  </si>
+  <si>
+    <t>COLONIA</t>
+  </si>
+  <si>
+    <t>COLONIA 18 JUL.</t>
+  </si>
+  <si>
+    <t>COLONIA GARIBALDI</t>
+  </si>
+  <si>
+    <t>COLONIA ITAPEBI</t>
+  </si>
+  <si>
+    <t>COLONIA LAVALLE</t>
+  </si>
+  <si>
+    <t>COLONIA NICOLIC</t>
+  </si>
+  <si>
+    <t>CONCHILLAS</t>
+  </si>
+  <si>
+    <t>CONSTANCIA</t>
+  </si>
+  <si>
+    <t>CONSTITUCION</t>
+  </si>
+  <si>
+    <t>COSMOPOLITA</t>
+  </si>
+  <si>
+    <t>COSTA AZUL1</t>
+  </si>
+  <si>
+    <t>COSTA AZUL2</t>
+  </si>
+  <si>
+    <t>CRUZ DE CAMINOS</t>
+  </si>
+  <si>
+    <t>CUARO</t>
+  </si>
+  <si>
+    <t>CUARÓ</t>
+  </si>
+  <si>
+    <t>CUARO CHICO</t>
+  </si>
+  <si>
+    <t>CUCHILLA ALTA</t>
+  </si>
+  <si>
+    <t>CUCHILLA DEL OMBU</t>
+  </si>
+  <si>
+    <t>CUFRE</t>
+  </si>
+  <si>
+    <t>CURTINA</t>
+  </si>
+  <si>
+    <t>DAYMAN</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>DURAZNO</t>
+  </si>
+  <si>
+    <t>E.MARTINEZ</t>
+  </si>
+  <si>
+    <t>ECILDA PAULIER</t>
+  </si>
+  <si>
+    <t>EGAÑA</t>
+  </si>
+  <si>
+    <t>EL BELLACO</t>
+  </si>
+  <si>
+    <t>EL CHORRO</t>
+  </si>
+  <si>
+    <t>EL EUCALIPTO</t>
+  </si>
+  <si>
+    <t>EL PINAR - SUR</t>
+  </si>
+  <si>
+    <t>EL TALA</t>
+  </si>
+  <si>
+    <t>EL TESORO</t>
+  </si>
+  <si>
+    <t>ESPERANZA</t>
+  </si>
+  <si>
+    <t>EST.ATLANTIDA</t>
+  </si>
+  <si>
+    <t>EST.LA FLORESTA</t>
+  </si>
+  <si>
+    <t>ESTANZUELA</t>
+  </si>
+  <si>
+    <t>F.MARCOS</t>
+  </si>
+  <si>
+    <t>F.STA.ROSA</t>
+  </si>
+  <si>
+    <t>FCIO. SANCHEZ</t>
+  </si>
+  <si>
+    <t>FEDERACION</t>
+  </si>
+  <si>
+    <t>FELICIANO</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>FLORIDA</t>
+  </si>
+  <si>
+    <t>FOMENTO</t>
+  </si>
+  <si>
+    <t>FRAILE MUERTO</t>
+  </si>
+  <si>
+    <t>FRAY BENTOS</t>
+  </si>
+  <si>
+    <t>FUNDACION POLANCO</t>
+  </si>
+  <si>
+    <t>G.AZNARES</t>
+  </si>
+  <si>
+    <t>GALLINAL</t>
+  </si>
+  <si>
+    <t>GARZON</t>
+  </si>
+  <si>
+    <t>GOMENSORO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOÑI</t>
+  </si>
+  <si>
+    <t>GUAYUVIRA</t>
+  </si>
+  <si>
+    <t>GUAZUBIRA</t>
+  </si>
+  <si>
+    <t>GUAZUBIRA VIEJO</t>
+  </si>
+  <si>
+    <t>GUICHON</t>
+  </si>
+  <si>
+    <t>I. CORTINAS</t>
+  </si>
+  <si>
+    <t>ILLESCAS</t>
+  </si>
+  <si>
+    <t>INDEPENDENCIA</t>
+  </si>
+  <si>
+    <t>ISIDORO NOBLIA</t>
+  </si>
+  <si>
+    <t>ISLA PATRULLA</t>
+  </si>
+  <si>
+    <t>ITUZAINGO</t>
+  </si>
+  <si>
+    <t>J.J. CASTRO</t>
+  </si>
+  <si>
+    <t>J.LACAZE</t>
+  </si>
+  <si>
+    <t>J.P.VARELA</t>
+  </si>
+  <si>
+    <t>JACKSON</t>
+  </si>
+  <si>
+    <t>JOANICO</t>
+  </si>
+  <si>
+    <t>JOSE IGNACIO</t>
+  </si>
+  <si>
+    <t>JOSE IGNACIO (ADCL)</t>
+  </si>
+  <si>
+    <t>JUAN SOLER</t>
+  </si>
+  <si>
+    <t>KILOMETRO 110</t>
+  </si>
+  <si>
+    <t>KIYU</t>
+  </si>
+  <si>
+    <t>L.GEIRES</t>
+  </si>
+  <si>
+    <t>LA AGUADA</t>
+  </si>
+  <si>
+    <t>LA ALDEA</t>
+  </si>
+  <si>
+    <t>LA BARRA</t>
+  </si>
+  <si>
+    <t>LA BOLSA</t>
+  </si>
+  <si>
+    <t>LA BOTA</t>
+  </si>
+  <si>
+    <t>LA BOTA ZB</t>
+  </si>
+  <si>
+    <t>LA BOYADA</t>
+  </si>
+  <si>
+    <t>LA CALERA</t>
+  </si>
+  <si>
+    <t>LA CALZADA</t>
+  </si>
+  <si>
+    <t>LA CAPUERA</t>
+  </si>
+  <si>
+    <t>LA CAPUERA (ZB)</t>
+  </si>
+  <si>
+    <t>LA CASILLA</t>
+  </si>
+  <si>
+    <t>LA CONCORDIA</t>
+  </si>
+  <si>
+    <t>LA CORONILLA</t>
+  </si>
+  <si>
+    <t>LA CRUZ</t>
+  </si>
+  <si>
+    <t>LA CUCHILLA</t>
+  </si>
+  <si>
+    <t>LA FLORESTA</t>
+  </si>
+  <si>
+    <t>LA HILERA</t>
+  </si>
+  <si>
+    <t>LA JUANITA</t>
+  </si>
+  <si>
+    <t>LA MACANA</t>
+  </si>
+  <si>
+    <t>LA MICAELA</t>
+  </si>
+  <si>
+    <t>LA PALMA</t>
+  </si>
+  <si>
+    <t>LA PALOMA1</t>
+  </si>
+  <si>
+    <t>LA PALOMA2</t>
+  </si>
+  <si>
+    <t>LA PAZ1</t>
+  </si>
+  <si>
+    <t>LA PAZ2</t>
+  </si>
+  <si>
+    <t>LA PEDRERA</t>
+  </si>
+  <si>
+    <t>LA PUENTE</t>
+  </si>
+  <si>
+    <t>LA TENTACION</t>
+  </si>
+  <si>
+    <t>LA TUNA</t>
+  </si>
+  <si>
+    <t>LAGO MERIN</t>
+  </si>
+  <si>
+    <t>LAGOMAR NORTE</t>
+  </si>
+  <si>
+    <t>LAGOMAR SUR</t>
+  </si>
+  <si>
+    <t>LAGUNA DE ROCHA</t>
+  </si>
+  <si>
+    <t>LAMAS</t>
+  </si>
+  <si>
+    <t>LAS CHILCAS</t>
+  </si>
+  <si>
+    <t>LAS FLORES</t>
+  </si>
+  <si>
+    <t>LAS PAJAS</t>
+  </si>
+  <si>
+    <t>LAS PALMAS</t>
+  </si>
+  <si>
+    <t>LAS PIEDRAS</t>
+  </si>
+  <si>
+    <t>LAS TOSCAS NORT</t>
+  </si>
+  <si>
+    <t>LAS TOSCAS1</t>
+  </si>
+  <si>
+    <t>LAS TOSCAS2</t>
+  </si>
+  <si>
+    <t>LAS VEGAS NORTE</t>
+  </si>
+  <si>
+    <t>LAS VEGAS SUR</t>
+  </si>
+  <si>
+    <t>LASCANO</t>
+  </si>
+  <si>
+    <t>LAURELES</t>
+  </si>
+  <si>
+    <t>LIBERTAD</t>
+  </si>
+  <si>
+    <t>LOMAS D SOLYMAR</t>
+  </si>
+  <si>
+    <t>LOMAS NORTE</t>
+  </si>
+  <si>
+    <t>LOMAS SOLYMAR 3</t>
+  </si>
+  <si>
+    <t>LOS CERROS</t>
+  </si>
+  <si>
+    <t>LOS CUADRADOS</t>
+  </si>
+  <si>
+    <t>LOS FEOS</t>
+  </si>
+  <si>
+    <t>LOS FURTADOS</t>
+  </si>
+  <si>
+    <t>LOS HIGUERONES</t>
+  </si>
+  <si>
+    <t>LOS PINOS</t>
+  </si>
+  <si>
+    <t>LOS SEMPER</t>
+  </si>
+  <si>
+    <t>LOS TALAS</t>
+  </si>
+  <si>
+    <t>LOS TITANES</t>
+  </si>
+  <si>
+    <t>M ALBINA</t>
+  </si>
+  <si>
+    <t>M.CHICO</t>
+  </si>
+  <si>
+    <t>M.CORAL</t>
+  </si>
+  <si>
+    <t>M.DE CORRALES</t>
+  </si>
+  <si>
+    <t>M.GRANDE</t>
+  </si>
+  <si>
+    <t>MACIEL</t>
+  </si>
+  <si>
+    <t>MAL ABRIGO</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MALDONADO (ZB)</t>
+  </si>
+  <si>
+    <t>MALVAREZ</t>
+  </si>
+  <si>
+    <t>MANANTIALES</t>
+  </si>
+  <si>
+    <t>MANGRULLO</t>
+  </si>
+  <si>
+    <t>MARGAT</t>
+  </si>
+  <si>
+    <t>MARINDIA</t>
+  </si>
+  <si>
+    <t>MARISCALA</t>
+  </si>
+  <si>
+    <t>MASOLLER</t>
+  </si>
+  <si>
+    <t>MEDANOS NORTE</t>
+  </si>
+  <si>
+    <t>MEDANOS SOLYMAR</t>
+  </si>
+  <si>
+    <t>MELLIZOS</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
+    <t>MERCEDES</t>
+  </si>
+  <si>
+    <t>MERINOS</t>
+  </si>
+  <si>
+    <t>MIGUEZ</t>
+  </si>
+  <si>
+    <t>MINAS</t>
+  </si>
+  <si>
+    <t>MOIRONES</t>
+  </si>
+  <si>
+    <t>MONTES</t>
+  </si>
+  <si>
+    <t>MONTES SOLYMAR</t>
+  </si>
+  <si>
+    <t>MONTEVIDEO</t>
+  </si>
+  <si>
+    <t>MONTVIDEO CHICO</t>
+  </si>
+  <si>
+    <t>MORATO</t>
+  </si>
+  <si>
+    <t>N.HELVECIA</t>
+  </si>
+  <si>
+    <t>N.PALMIRA</t>
+  </si>
+  <si>
+    <t>NEPTUNIA NORTE</t>
+  </si>
+  <si>
+    <t>NEPTUNIA SUR</t>
+  </si>
+  <si>
+    <t>NUEVA CARRARA</t>
+  </si>
+  <si>
+    <t>NUEVO BERLIN</t>
+  </si>
+  <si>
+    <t>O.DE LAVALLE</t>
+  </si>
+  <si>
+    <t>O.DE ORIBE</t>
+  </si>
+  <si>
+    <t>OCEAN PARK</t>
+  </si>
+  <si>
+    <t>ORGOROZO</t>
+  </si>
+  <si>
+    <t>P. CASTELLANOS</t>
+  </si>
+  <si>
+    <t>P.AZUCAR</t>
+  </si>
+  <si>
+    <t>P.CERRO</t>
+  </si>
+  <si>
+    <t>P.D.PLATA NORTE</t>
+  </si>
+  <si>
+    <t>P.DE PACHE</t>
+  </si>
+  <si>
+    <t>P.DEL PLATA</t>
+  </si>
+  <si>
+    <t>P.DEL.ESTE</t>
+  </si>
+  <si>
+    <t>P.SEVERINO</t>
+  </si>
+  <si>
+    <t>P.SOLA</t>
+  </si>
+  <si>
+    <t>P.TOROS</t>
+  </si>
+  <si>
+    <t>PALMITAS</t>
+  </si>
+  <si>
+    <t>PALO SOLO</t>
+  </si>
+  <si>
+    <t>PANDO</t>
+  </si>
+  <si>
+    <t>PANDULE</t>
+  </si>
+  <si>
+    <t>PARAJE PENSE</t>
+  </si>
+  <si>
+    <t>PARALLÉ</t>
+  </si>
+  <si>
+    <t>PARQUE MIRAMAR</t>
+  </si>
+  <si>
+    <t>PARQUE SOLYMAR</t>
+  </si>
+  <si>
+    <t>PASANO</t>
+  </si>
+  <si>
+    <t>PASO ARRIERA</t>
+  </si>
+  <si>
+    <t>PASO ATAQUES</t>
+  </si>
+  <si>
+    <t>PASO CARRASCO</t>
+  </si>
+  <si>
+    <t>PASO D PARQUE</t>
+  </si>
+  <si>
+    <t>PASO DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PASO DE LAS CARRETAS</t>
+  </si>
+  <si>
+    <t>PASO DE LOS NOVILLOS</t>
+  </si>
+  <si>
+    <t>PASO DEL MEDIO</t>
+  </si>
+  <si>
+    <t>PASO DEL TAPADO</t>
+  </si>
+  <si>
+    <t>PASO FARIAS</t>
+  </si>
+  <si>
+    <t>PASO HOSPITAL</t>
+  </si>
+  <si>
+    <t>PASO PEREIRA</t>
+  </si>
+  <si>
+    <t>PAYSANDU</t>
+  </si>
+  <si>
+    <t>PBLO. FERNANDEZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PIEDRA DEL TORO</t>
+  </si>
+  <si>
+    <t>PIEDRAS.COLORA.</t>
+  </si>
+  <si>
+    <t>PINAMAR NORTE</t>
+  </si>
+  <si>
+    <t>PINAMAR SUR</t>
+  </si>
+  <si>
+    <t>PINAR - NORTE</t>
+  </si>
+  <si>
+    <t>PINARES</t>
+  </si>
+  <si>
+    <t>PINARES - ATL</t>
+  </si>
+  <si>
+    <t>PINTADO</t>
+  </si>
+  <si>
+    <t>PINTADO GRANDE</t>
+  </si>
+  <si>
+    <t>PIÑERA</t>
+  </si>
+  <si>
+    <t>PIRARAJA</t>
+  </si>
+  <si>
+    <t>PIRIAPOLIS</t>
+  </si>
+  <si>
+    <t>PIRIAPOLIS INT</t>
+  </si>
+  <si>
+    <t>PLACIDO ROSAS</t>
+  </si>
+  <si>
+    <t>POBLADO ALONSO</t>
+  </si>
+  <si>
+    <t>POBLADO EL ORO</t>
+  </si>
+  <si>
+    <t>POBLADO URUGUAY</t>
+  </si>
+  <si>
+    <t>POLANCO DEL YI</t>
+  </si>
+  <si>
+    <t>POLANCO LAVALLEJA</t>
+  </si>
+  <si>
+    <t>PORVENIR</t>
+  </si>
+  <si>
+    <t>PROGRESO</t>
+  </si>
+  <si>
+    <t>PTA. DE VALDEZ</t>
+  </si>
+  <si>
+    <t>PTA. DEL DIABLO</t>
+  </si>
+  <si>
+    <t>PUEBLO AREVALO</t>
+  </si>
+  <si>
+    <t>PUEBLO CASTILLO</t>
+  </si>
+  <si>
+    <t>PUEBLO CELESTE</t>
+  </si>
+  <si>
+    <t>PUEBLO COLON</t>
+  </si>
+  <si>
+    <t>PUEBLO DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>PUEBLO DEL BARRO</t>
+  </si>
+  <si>
+    <t>PUEBLO EDEN</t>
+  </si>
+  <si>
+    <t>PUEBLO GRECO</t>
+  </si>
+  <si>
+    <t>PUEBLO HERIBERTO</t>
+  </si>
+  <si>
+    <t>PUEBLO LA BOLSA</t>
+  </si>
+  <si>
+    <t>PUEBLO NUEVO</t>
+  </si>
+  <si>
+    <t>PUEBLO SOTO</t>
+  </si>
+  <si>
+    <t>PUEBLO ZEBALLOS</t>
+  </si>
+  <si>
+    <t>PUENTE DE VALIZAS</t>
+  </si>
+  <si>
+    <t>PUIMAYEN</t>
+  </si>
+  <si>
+    <t>PUNTA 5 SAUCES</t>
+  </si>
+  <si>
+    <t>PUNTA BALLENA</t>
+  </si>
+  <si>
+    <t>PUNTA RUBIA</t>
+  </si>
+  <si>
+    <t>PUNTAS DEL PARAO</t>
+  </si>
+  <si>
+    <t>QUEBRACHO</t>
+  </si>
+  <si>
+    <t>QUEGUAY CHICO</t>
+  </si>
+  <si>
+    <t>QUEGUAYAR</t>
+  </si>
+  <si>
+    <t>RADIAL</t>
+  </si>
+  <si>
+    <t>RAFAEL PERAZZA</t>
+  </si>
+  <si>
+    <t>RAIGON</t>
+  </si>
+  <si>
+    <t>REBOLEDO</t>
+  </si>
+  <si>
+    <t>RIACHUELO</t>
+  </si>
+  <si>
+    <t>RINCON</t>
+  </si>
+  <si>
+    <t>RINCON DE PACHECO</t>
+  </si>
+  <si>
+    <t>RINCON DE PINTADO</t>
+  </si>
+  <si>
+    <t>RINCON DEL PINO</t>
+  </si>
+  <si>
+    <t>RINCON PEREIRA</t>
+  </si>
+  <si>
+    <t>RIO BRANCO</t>
+  </si>
+  <si>
+    <t>RISSO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>RODO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROSARIO</t>
+  </si>
+  <si>
+    <t>S.ANTONIO</t>
+  </si>
+  <si>
+    <t>S.BAUTISTA</t>
+  </si>
+  <si>
+    <t>S.DEL YI</t>
+  </si>
+  <si>
+    <t>S.GRANDE</t>
+  </si>
+  <si>
+    <t>S.GREGORIO</t>
+  </si>
+  <si>
+    <t>S.JACINTO</t>
+  </si>
+  <si>
+    <t>S.JORGE</t>
+  </si>
+  <si>
+    <t>S.RAMON</t>
+  </si>
+  <si>
+    <t>SACACHISPAS</t>
+  </si>
+  <si>
+    <t>SALINAS</t>
+  </si>
+  <si>
+    <t>SALTO</t>
+  </si>
+  <si>
+    <t>SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>SAN BENITO</t>
+  </si>
+  <si>
+    <t>SAN CARLOS</t>
+  </si>
+  <si>
+    <t>SAN CRISTOBAL</t>
+  </si>
+  <si>
+    <t>SAN GABRIEL</t>
+  </si>
+  <si>
+    <t>SAN GREGORIO</t>
+  </si>
+  <si>
+    <t>SAN JAVIER</t>
+  </si>
+  <si>
+    <t>SAN JOSE</t>
+  </si>
+  <si>
+    <t>SAN LUIS</t>
+  </si>
+  <si>
+    <t>SAN LUIS(CNLNES)</t>
+  </si>
+  <si>
+    <t>SAN PEDRO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANTA ANA</t>
+  </si>
+  <si>
+    <t>SANTA ANA C</t>
+  </si>
+  <si>
+    <t>SANTA CLARA</t>
+  </si>
+  <si>
+    <t>SANTA MONICA</t>
+  </si>
+  <si>
+    <t>SANTA TERESITA</t>
+  </si>
+  <si>
+    <t>SAU.DEL YI</t>
+  </si>
+  <si>
+    <t>SAUCE</t>
+  </si>
+  <si>
+    <t>SAUCE DE BATOVI</t>
+  </si>
+  <si>
+    <t>SAUCE DE PORTEZUELO</t>
+  </si>
+  <si>
+    <t>SAUCE.</t>
+  </si>
+  <si>
+    <t>SDI. DE NAVARRO</t>
+  </si>
+  <si>
+    <t>SEQUEIRA</t>
+  </si>
+  <si>
+    <t>SHANGRILA</t>
+  </si>
+  <si>
+    <t>SJ.CARRASCO NOR</t>
+  </si>
+  <si>
+    <t>SJ.CARRASCO SUR</t>
+  </si>
+  <si>
+    <t>SOCA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>SOLIS DE MATAOJ</t>
+  </si>
+  <si>
+    <t>SOLYMAR NORTE</t>
+  </si>
+  <si>
+    <t>SOLYMAR SUR</t>
+  </si>
+  <si>
+    <t>SOUDRIERS</t>
+  </si>
+  <si>
+    <t>STA. CATALINA</t>
+  </si>
+  <si>
+    <t>STA. LUCIA DEL ESTE</t>
+  </si>
+  <si>
+    <t>STA. ROSA</t>
+  </si>
+  <si>
+    <t>STA.LUCIA</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>T.TRES</t>
+  </si>
+  <si>
+    <t>TACUAREMBO</t>
+  </si>
+  <si>
+    <t>TALA</t>
+  </si>
+  <si>
+    <t>TAMBORES</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
+    <t>TARARIRAS</t>
+  </si>
+  <si>
+    <t>TARUMAN</t>
+  </si>
+  <si>
+    <t>TIATUCURA</t>
+  </si>
+  <si>
+    <t>TIERR COLORADAS</t>
+  </si>
+  <si>
+    <t>TOLEDO</t>
+  </si>
+  <si>
+    <t>TOPADOR</t>
+  </si>
+  <si>
+    <t>TOTORAL D SAUCE</t>
+  </si>
+  <si>
+    <t>TRANQUERAS</t>
+  </si>
+  <si>
+    <t>TRES ISLAS</t>
+  </si>
+  <si>
+    <t>TRINIDAD</t>
+  </si>
+  <si>
+    <t>TUPAMBAE</t>
+  </si>
+  <si>
+    <t>V.ANSINA</t>
+  </si>
+  <si>
+    <t>V.ARGENTINA</t>
+  </si>
+  <si>
+    <t>V.CARMEN</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
+    <t>VALENTINES</t>
+  </si>
+  <si>
+    <t>VALLE SOBA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>VERGARA</t>
+  </si>
+  <si>
+    <t>VIANA</t>
+  </si>
+  <si>
+    <t>VICHADERO</t>
+  </si>
+  <si>
+    <t>VILLA MARIA</t>
+  </si>
+  <si>
+    <t>VILLA MONTAÑESA</t>
+  </si>
+  <si>
+    <t>VILLA OLMOS</t>
+  </si>
+  <si>
+    <t>VILLA SARA</t>
+  </si>
+  <si>
+    <t>VILLA SORIANO</t>
+  </si>
+  <si>
+    <t>YOUNG</t>
+  </si>
+  <si>
+    <t>ZAPICAN</t>
   </si>
   <si>
     <t>System URI</t>
@@ -233,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -330,20 +1701,28 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>24</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -353,7 +1732,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B459"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -362,28 +1741,3674 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B231" t="s" s="2">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B238" t="s" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B239" t="s" s="2">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B241" t="s" s="2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B243" t="s" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B256" t="s" s="2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B257" t="s" s="2">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B265" t="s" s="2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B268" t="s" s="2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B272" t="s" s="2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B274" t="s" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B275" t="s" s="2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="B276" t="s" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B277" t="s" s="2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B278" t="s" s="2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B279" t="s" s="2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B280" t="s" s="2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B281" t="s" s="2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B285" t="s" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B286" t="s" s="2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B287" t="s" s="2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B288" t="s" s="2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B289" t="s" s="2">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B290" t="s" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B292" t="s" s="2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B293" t="s" s="2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B294" t="s" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="B295" t="s" s="2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B296" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B297" t="s" s="2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="B298" t="s" s="2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="B299" t="s" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B300" t="s" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="B301" t="s" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B302" t="s" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B303" t="s" s="2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B304" t="s" s="2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B305" t="s" s="2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B306" t="s" s="2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B307" t="s" s="2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B308" t="s" s="2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B309" t="s" s="2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B310" t="s" s="2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B311" t="s" s="2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B312" t="s" s="2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B313" t="s" s="2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B314" t="s" s="2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B315" t="s" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B316" t="s" s="2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B317" t="s" s="2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B318" t="s" s="2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B319" t="s" s="2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B320" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B321" t="s" s="2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B322" t="s" s="2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B323" t="s" s="2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B324" t="s" s="2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B325" t="s" s="2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B326" t="s" s="2">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B327" t="s" s="2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="B328" t="s" s="2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B329" t="s" s="2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B330" t="s" s="2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B331" t="s" s="2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B332" t="s" s="2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B333" t="s" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B334" t="s" s="2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B335" t="s" s="2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B336" t="s" s="2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B337" t="s" s="2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B338" t="s" s="2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B339" t="s" s="2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B340" t="s" s="2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B341" t="s" s="2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B342" t="s" s="2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B343" t="s" s="2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B344" t="s" s="2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B345" t="s" s="2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B346" t="s" s="2">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B347" t="s" s="2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B348" t="s" s="2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B349" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B350" t="s" s="2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B351" t="s" s="2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B352" t="s" s="2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B353" t="s" s="2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B354" t="s" s="2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B355" t="s" s="2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B356" t="s" s="2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B357" t="s" s="2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B358" t="s" s="2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B359" t="s" s="2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B360" t="s" s="2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B361" t="s" s="2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B362" t="s" s="2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B363" t="s" s="2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B364" t="s" s="2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B365" t="s" s="2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B366" t="s" s="2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B367" t="s" s="2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B368" t="s" s="2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B369" t="s" s="2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B370" t="s" s="2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B371" t="s" s="2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B372" t="s" s="2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B373" t="s" s="2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B374" t="s" s="2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B375" t="s" s="2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B376" t="s" s="2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B377" t="s" s="2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B378" t="s" s="2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B379" t="s" s="2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B380" t="s" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B381" t="s" s="2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B382" t="s" s="2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B383" t="s" s="2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B384" t="s" s="2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B385" t="s" s="2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B386" t="s" s="2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B387" t="s" s="2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B388" t="s" s="2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B389" t="s" s="2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B390" t="s" s="2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B391" t="s" s="2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B392" t="s" s="2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B393" t="s" s="2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B394" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B395" t="s" s="2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="B396" t="s" s="2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="B397" t="s" s="2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B398" t="s" s="2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="B399" t="s" s="2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B400" t="s" s="2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="B401" t="s" s="2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B402" t="s" s="2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B403" t="s" s="2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B404" t="s" s="2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B405" t="s" s="2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B406" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B407" t="s" s="2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="B408" t="s" s="2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B409" t="s" s="2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B410" t="s" s="2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B411" t="s" s="2">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B412" t="s" s="2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B413" t="s" s="2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B414" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B415" t="s" s="2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B416" t="s" s="2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B417" t="s" s="2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B418" t="s" s="2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B419" t="s" s="2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B420" t="s" s="2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B421" t="s" s="2">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B422" t="s" s="2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B423" t="s" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B424" t="s" s="2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B425" t="s" s="2">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B426" t="s" s="2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B427" t="s" s="2">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B428" t="s" s="2">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B429" t="s" s="2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B430" t="s" s="2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B431" t="s" s="2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B432" t="s" s="2">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B433" t="s" s="2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B434" t="s" s="2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B435" t="s" s="2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B436" t="s" s="2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B437" t="s" s="2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B438" t="s" s="2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B439" t="s" s="2">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B440" t="s" s="2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B441" t="s" s="2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B442" t="s" s="2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B443" t="s" s="2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B444" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B445" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B446" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B447" t="s" s="2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B448" t="s" s="2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B449" t="s" s="2">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B450" t="s" s="2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B451" t="s" s="2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B452" t="s" s="2">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B453" t="s" s="2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B454" t="s" s="2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B455" t="s" s="2">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B456" t="s" s="2">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B457" t="s" s="2">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B458" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B459" t="s" s="2">
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/site/ValueSet-vs-localidades-uy.xlsx
+++ b/site/ValueSet-vs-localidades-uy.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
